--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202606/AllSymbols_P&L_20260608.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202606/AllSymbols_P&L_20260608.xlsx
@@ -648,13 +648,13 @@
         <v>2000</v>
       </c>
       <c r="C2">
-        <v>35.92</v>
+        <v>35.38</v>
       </c>
       <c r="D2">
-        <v>-15.32</v>
+        <v>-137.81</v>
       </c>
       <c r="E2">
-        <v>71840</v>
+        <v>70760</v>
       </c>
       <c r="F2" t="s">
         <v>71</v>
@@ -663,10 +663,10 @@
         <v>75</v>
       </c>
       <c r="H2">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I2">
-        <v>9173.969999999999</v>
+        <v>9028.98</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -677,13 +677,13 @@
         <v>471000</v>
       </c>
       <c r="C3">
-        <v>14.57</v>
+        <v>13.38</v>
       </c>
       <c r="D3">
-        <v>-15632.02</v>
+        <v>-71518.52</v>
       </c>
       <c r="E3">
-        <v>6862470</v>
+        <v>6301980</v>
       </c>
       <c r="F3" t="s">
         <v>71</v>
@@ -692,10 +692,10 @@
         <v>75</v>
       </c>
       <c r="H3">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I3">
-        <v>876337.42</v>
+        <v>804132.65</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -706,13 +706,13 @@
         <v>6000</v>
       </c>
       <c r="C4">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="D4">
-        <v>15.32</v>
+        <v>-7.66</v>
       </c>
       <c r="E4">
-        <v>34980</v>
+        <v>34920</v>
       </c>
       <c r="F4" t="s">
         <v>71</v>
@@ -721,10 +721,10 @@
         <v>75</v>
       </c>
       <c r="H4">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I4">
-        <v>4466.95</v>
+        <v>4455.79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -735,13 +735,13 @@
         <v>1306000</v>
       </c>
       <c r="C5">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="D5">
-        <v>18338.2</v>
+        <v>16664.56</v>
       </c>
       <c r="E5">
-        <v>8919980</v>
+        <v>9050580</v>
       </c>
       <c r="F5" t="s">
         <v>71</v>
@@ -750,10 +750,10 @@
         <v>75</v>
       </c>
       <c r="H5">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I5">
-        <v>1139081.45</v>
+        <v>1154854.01</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -764,13 +764,13 @@
         <v>2000</v>
       </c>
       <c r="C6">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="D6">
-        <v>163.39</v>
+        <v>-127.6</v>
       </c>
       <c r="E6">
-        <v>71800</v>
+        <v>70800</v>
       </c>
       <c r="F6" t="s">
         <v>71</v>
@@ -779,10 +779,10 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I6">
-        <v>9168.860000000001</v>
+        <v>9034.08</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -793,13 +793,13 @@
         <v>200</v>
       </c>
       <c r="C7">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="D7">
-        <v>-14.81</v>
+        <v>-10.72</v>
       </c>
       <c r="E7">
-        <v>5560</v>
+        <v>5476</v>
       </c>
       <c r="F7" t="s">
         <v>71</v>
@@ -808,10 +808,10 @@
         <v>75</v>
       </c>
       <c r="H7">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I7">
-        <v>710.01</v>
+        <v>698.74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -822,13 +822,13 @@
         <v>300</v>
       </c>
       <c r="C8">
-        <v>124.5</v>
+        <v>121.3</v>
       </c>
       <c r="D8">
-        <v>38.3</v>
+        <v>-122.5</v>
       </c>
       <c r="E8">
-        <v>37350</v>
+        <v>36390</v>
       </c>
       <c r="F8" t="s">
         <v>71</v>
@@ -837,10 +837,10 @@
         <v>75</v>
       </c>
       <c r="H8">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I8">
-        <v>4769.6</v>
+        <v>4643.36</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -851,13 +851,13 @@
         <v>2000</v>
       </c>
       <c r="C9">
-        <v>25.28</v>
+        <v>24.98</v>
       </c>
       <c r="D9">
-        <v>-66.38</v>
+        <v>-76.56</v>
       </c>
       <c r="E9">
-        <v>50560</v>
+        <v>49960</v>
       </c>
       <c r="F9" t="s">
         <v>71</v>
@@ -866,10 +866,10 @@
         <v>75</v>
       </c>
       <c r="H9">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I9">
-        <v>6456.51</v>
+        <v>6374.9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -880,13 +880,13 @@
         <v>600</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>85.88</v>
       </c>
       <c r="D10">
-        <v>-33.7</v>
+        <v>-85.75</v>
       </c>
       <c r="E10">
-        <v>52200</v>
+        <v>51528</v>
       </c>
       <c r="F10" t="s">
         <v>71</v>
@@ -895,10 +895,10 @@
         <v>75</v>
       </c>
       <c r="H10">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I10">
-        <v>6665.94</v>
+        <v>6574.97</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -909,13 +909,13 @@
         <v>210000</v>
       </c>
       <c r="C11">
-        <v>32.96</v>
+        <v>31.56</v>
       </c>
       <c r="D11">
-        <v>-9650.34</v>
+        <v>-37514.4</v>
       </c>
       <c r="E11">
-        <v>6921600</v>
+        <v>6627600</v>
       </c>
       <c r="F11" t="s">
         <v>71</v>
@@ -924,10 +924,10 @@
         <v>75</v>
       </c>
       <c r="H11">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I11">
-        <v>883888.3199999999</v>
+        <v>845681.76</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -938,13 +938,13 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>10.27</v>
+        <v>10.01</v>
       </c>
       <c r="D12">
-        <v>-17.87</v>
+        <v>-23.22</v>
       </c>
       <c r="E12">
-        <v>7189</v>
+        <v>7007</v>
       </c>
       <c r="F12" t="s">
         <v>71</v>
@@ -953,10 +953,10 @@
         <v>75</v>
       </c>
       <c r="H12">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I12">
-        <v>918.04</v>
+        <v>894.09</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -967,13 +967,13 @@
         <v>4700</v>
       </c>
       <c r="C13">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="D13">
-        <v>-7499.44</v>
+        <v>-16792.16</v>
       </c>
       <c r="E13">
-        <v>3341700</v>
+        <v>3210100</v>
       </c>
       <c r="F13" t="s">
         <v>71</v>
@@ -982,10 +982,10 @@
         <v>75</v>
       </c>
       <c r="H13">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I13">
-        <v>426735.09</v>
+        <v>409608.76</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -996,13 +996,13 @@
         <v>33000</v>
       </c>
       <c r="C14">
-        <v>396.4</v>
+        <v>386.8</v>
       </c>
       <c r="D14">
-        <v>-18534.78</v>
+        <v>-40423.68</v>
       </c>
       <c r="E14">
-        <v>13081200</v>
+        <v>12764400</v>
       </c>
       <c r="F14" t="s">
         <v>71</v>
@@ -1011,10 +1011,10 @@
         <v>75</v>
       </c>
       <c r="H14">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I14">
-        <v>1670469.24</v>
+        <v>1628737.44</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1025,13 +1025,13 @@
         <v>4000</v>
       </c>
       <c r="C15">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="D15">
-        <v>30.64</v>
+        <v>25.52</v>
       </c>
       <c r="E15">
-        <v>21240</v>
+        <v>21440</v>
       </c>
       <c r="F15" t="s">
         <v>71</v>
@@ -1040,10 +1040,10 @@
         <v>75</v>
       </c>
       <c r="H15">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I15">
-        <v>2712.35</v>
+        <v>2735.74</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1054,13 +1054,13 @@
         <v>35300</v>
       </c>
       <c r="C16">
-        <v>6739</v>
+        <v>6555</v>
       </c>
       <c r="D16">
-        <v>-47560.45</v>
+        <v>-40550.18</v>
       </c>
       <c r="E16">
-        <v>237886700</v>
+        <v>231391500</v>
       </c>
       <c r="F16" t="s">
         <v>72</v>
@@ -1072,7 +1072,7 @@
         <v>0.0062</v>
       </c>
       <c r="I16">
-        <v>1474897.54</v>
+        <v>1434627.3</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1083,13 +1083,13 @@
         <v>200</v>
       </c>
       <c r="C17">
-        <v>453.2</v>
+        <v>446.4</v>
       </c>
       <c r="D17">
-        <v>-148.07</v>
+        <v>-173.54</v>
       </c>
       <c r="E17">
-        <v>90640</v>
+        <v>89280</v>
       </c>
       <c r="F17" t="s">
         <v>71</v>
@@ -1098,10 +1098,10 @@
         <v>75</v>
       </c>
       <c r="H17">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I17">
-        <v>11574.73</v>
+        <v>11392.13</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1112,13 +1112,13 @@
         <v>16000</v>
       </c>
       <c r="C18">
-        <v>7.37</v>
+        <v>7.3</v>
       </c>
       <c r="D18">
-        <v>-183.82</v>
+        <v>-142.91</v>
       </c>
       <c r="E18">
-        <v>117920</v>
+        <v>116800</v>
       </c>
       <c r="F18" t="s">
         <v>71</v>
@@ -1127,10 +1127,10 @@
         <v>75</v>
       </c>
       <c r="H18">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I18">
-        <v>15058.38</v>
+        <v>14903.68</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1141,13 +1141,13 @@
         <v>2100</v>
       </c>
       <c r="C19">
-        <v>5920</v>
+        <v>5830</v>
       </c>
       <c r="D19">
-        <v>654.95</v>
+        <v>-1179.95</v>
       </c>
       <c r="E19">
-        <v>12432000</v>
+        <v>12243000</v>
       </c>
       <c r="F19" t="s">
         <v>72</v>
@@ -1159,7 +1159,7 @@
         <v>0.0062</v>
       </c>
       <c r="I19">
-        <v>77078.39999999999</v>
+        <v>75906.60000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1170,13 +1170,13 @@
         <v>1800</v>
       </c>
       <c r="C20">
-        <v>42.18</v>
+        <v>42.2</v>
       </c>
       <c r="D20">
-        <v>-147.05</v>
+        <v>4.59</v>
       </c>
       <c r="E20">
-        <v>75924</v>
+        <v>75960</v>
       </c>
       <c r="F20" t="s">
         <v>71</v>
@@ -1185,10 +1185,10 @@
         <v>75</v>
       </c>
       <c r="H20">
-        <v>0.1277</v>
+        <v>0.1276</v>
       </c>
       <c r="I20">
-        <v>9695.49</v>
+        <v>9692.5</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1199,13 +1199,13 @@
         <v>6000</v>
       </c>
       <c r="C21">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="D21">
-        <v>-139.45</v>
+        <v>-46.57</v>
       </c>
       <c r="E21">
-        <v>14820</v>
+        <v>14760</v>
       </c>
       <c r="F21" t="s">
         <v>73</v>
@@ -1214,10 +1214,10 @@
         <v>75</v>
       </c>
       <c r="H21">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I21">
-        <v>11481.05</v>
+        <v>11456.71</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1228,13 +1228,13 @@
         <v>13900</v>
       </c>
       <c r="C22">
-        <v>105.99</v>
+        <v>106.27</v>
       </c>
       <c r="D22">
-        <v>-48511</v>
+        <v>3892</v>
       </c>
       <c r="E22">
-        <v>1473261</v>
+        <v>1477153</v>
       </c>
       <c r="F22" t="s">
         <v>74</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1473261</v>
+        <v>1477153</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1257,13 +1257,13 @@
         <v>15675</v>
       </c>
       <c r="C23">
-        <v>91.23</v>
+        <v>93.23</v>
       </c>
       <c r="D23">
-        <v>-98595.75</v>
+        <v>31350</v>
       </c>
       <c r="E23">
-        <v>1430030.25</v>
+        <v>1461380.25</v>
       </c>
       <c r="F23" t="s">
         <v>74</v>
@@ -1275,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1430030.25</v>
+        <v>1461380.25</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1286,13 +1286,13 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>119.7</v>
+        <v>120.91</v>
       </c>
       <c r="D24">
-        <v>-17.5</v>
+        <v>12.1</v>
       </c>
       <c r="E24">
-        <v>1197</v>
+        <v>1209.1</v>
       </c>
       <c r="F24" t="s">
         <v>74</v>
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1197</v>
+        <v>1209.1</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1315,13 +1315,13 @@
         <v>7000</v>
       </c>
       <c r="C25">
-        <v>121.06</v>
+        <v>120.07</v>
       </c>
       <c r="D25">
-        <v>-34230</v>
+        <v>-6930</v>
       </c>
       <c r="E25">
-        <v>847420</v>
+        <v>840490</v>
       </c>
       <c r="F25" t="s">
         <v>74</v>
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>847420</v>
+        <v>840490</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1344,13 +1344,13 @@
         <v>70</v>
       </c>
       <c r="C26">
-        <v>15.9</v>
+        <v>16.85</v>
       </c>
       <c r="D26">
-        <v>-139.3</v>
+        <v>66.5</v>
       </c>
       <c r="E26">
-        <v>1113</v>
+        <v>1179.5</v>
       </c>
       <c r="F26" t="s">
         <v>74</v>
@@ -1362,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1113</v>
+        <v>1179.5</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1373,13 +1373,13 @@
         <v>3000</v>
       </c>
       <c r="C27">
-        <v>10.59</v>
+        <v>10.46</v>
       </c>
       <c r="D27">
-        <v>-162.69</v>
+        <v>-302.71</v>
       </c>
       <c r="E27">
-        <v>31770</v>
+        <v>31380</v>
       </c>
       <c r="F27" t="s">
         <v>73</v>
@@ -1388,10 +1388,10 @@
         <v>75</v>
       </c>
       <c r="H27">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I27">
-        <v>24612.22</v>
+        <v>24357.16</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1402,13 +1402,13 @@
         <v>821</v>
       </c>
       <c r="C28">
-        <v>185.95</v>
+        <v>187.46</v>
       </c>
       <c r="D28">
-        <v>-3793.84</v>
+        <v>1239.71</v>
       </c>
       <c r="E28">
-        <v>152664.95</v>
+        <v>153904.66</v>
       </c>
       <c r="F28" t="s">
         <v>74</v>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>152664.95</v>
+        <v>153904.66</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1431,13 +1431,13 @@
         <v>200</v>
       </c>
       <c r="C29">
-        <v>6.97</v>
+        <v>6.86</v>
       </c>
       <c r="D29">
-        <v>-12.4</v>
+        <v>-17.08</v>
       </c>
       <c r="E29">
-        <v>1394</v>
+        <v>1372</v>
       </c>
       <c r="F29" t="s">
         <v>73</v>
@@ -1446,10 +1446,10 @@
         <v>75</v>
       </c>
       <c r="H29">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I29">
-        <v>1079.93</v>
+        <v>1064.95</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1460,13 +1460,13 @@
         <v>15</v>
       </c>
       <c r="C30">
-        <v>254.83</v>
+        <v>250.67</v>
       </c>
       <c r="D30">
-        <v>-141.92</v>
+        <v>-62.4</v>
       </c>
       <c r="E30">
-        <v>3822.45</v>
+        <v>3760.05</v>
       </c>
       <c r="F30" t="s">
         <v>74</v>
@@ -1478,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>3822.45</v>
+        <v>3760.05</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1489,13 +1489,13 @@
         <v>706024</v>
       </c>
       <c r="C31">
-        <v>33.56</v>
+        <v>33.62</v>
       </c>
       <c r="D31">
-        <v>-529518</v>
+        <v>42361.44</v>
       </c>
       <c r="E31">
-        <v>23694165.44</v>
+        <v>23736526.88</v>
       </c>
       <c r="F31" t="s">
         <v>74</v>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>23694165.44</v>
+        <v>23736526.88</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1518,13 +1518,13 @@
         <v>29</v>
       </c>
       <c r="C32">
-        <v>257.4</v>
+        <v>252.03</v>
       </c>
       <c r="D32">
-        <v>38.86</v>
+        <v>-155.73</v>
       </c>
       <c r="E32">
-        <v>7464.6</v>
+        <v>7308.87</v>
       </c>
       <c r="F32" t="s">
         <v>74</v>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>7464.6</v>
+        <v>7308.87</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1547,13 +1547,13 @@
         <v>103455</v>
       </c>
       <c r="C33">
-        <v>55.34</v>
+        <v>53.92</v>
       </c>
       <c r="D33">
-        <v>-282949.43</v>
+        <v>-146906.1</v>
       </c>
       <c r="E33">
-        <v>5725199.7</v>
+        <v>5578293.6</v>
       </c>
       <c r="F33" t="s">
         <v>74</v>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>5725199.7</v>
+        <v>5578293.6</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1576,13 +1576,13 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>152.4</v>
+        <v>162.11</v>
       </c>
       <c r="D34">
-        <v>-58.65</v>
+        <v>48.55</v>
       </c>
       <c r="E34">
-        <v>762</v>
+        <v>810.55</v>
       </c>
       <c r="F34" t="s">
         <v>74</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>762</v>
+        <v>810.55</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1605,13 +1605,13 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <v>121.64</v>
+        <v>124.15</v>
       </c>
       <c r="D35">
-        <v>-108.68</v>
+        <v>32.63</v>
       </c>
       <c r="E35">
-        <v>1581.32</v>
+        <v>1613.95</v>
       </c>
       <c r="F35" t="s">
         <v>74</v>
@@ -1623,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1581.32</v>
+        <v>1613.95</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1634,13 +1634,13 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>179.85</v>
+        <v>173.645</v>
       </c>
       <c r="D36">
-        <v>-1.1</v>
+        <v>-62.05</v>
       </c>
       <c r="E36">
-        <v>1798.5</v>
+        <v>1736.45</v>
       </c>
       <c r="F36" t="s">
         <v>74</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>1798.5</v>
+        <v>1736.45</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1663,13 +1663,13 @@
         <v>800</v>
       </c>
       <c r="C37">
-        <v>63.78</v>
+        <v>62.76</v>
       </c>
       <c r="D37">
-        <v>-223.12</v>
+        <v>-633.37</v>
       </c>
       <c r="E37">
-        <v>51024</v>
+        <v>50208</v>
       </c>
       <c r="F37" t="s">
         <v>73</v>
@@ -1678,10 +1678,10 @@
         <v>75</v>
       </c>
       <c r="H37">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I37">
-        <v>39528.29</v>
+        <v>38971.45</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1692,13 +1692,13 @@
         <v>654826</v>
       </c>
       <c r="C38">
-        <v>30.66</v>
+        <v>30.87</v>
       </c>
       <c r="D38">
-        <v>-412540.38</v>
+        <v>137513.46</v>
       </c>
       <c r="E38">
-        <v>20076965.16</v>
+        <v>20214478.62</v>
       </c>
       <c r="F38" t="s">
         <v>74</v>
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>20076965.16</v>
+        <v>20214478.62</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1721,13 +1721,13 @@
         <v>5000</v>
       </c>
       <c r="C39">
-        <v>103.7</v>
+        <v>106.82</v>
       </c>
       <c r="D39">
-        <v>900</v>
+        <v>15600</v>
       </c>
       <c r="E39">
-        <v>518500</v>
+        <v>534100</v>
       </c>
       <c r="F39" t="s">
         <v>74</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>518500</v>
+        <v>534100</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="C40">
-        <v>102.26</v>
+        <v>102.88</v>
       </c>
       <c r="D40">
-        <v>-2.69</v>
+        <v>0.62</v>
       </c>
       <c r="E40">
-        <v>102.26</v>
+        <v>102.88</v>
       </c>
       <c r="F40" t="s">
         <v>74</v>
@@ -1768,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>102.26</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1779,13 +1779,13 @@
         <v>36</v>
       </c>
       <c r="C41">
-        <v>138.12</v>
+        <v>139.07</v>
       </c>
       <c r="D41">
-        <v>-141.84</v>
+        <v>34.2</v>
       </c>
       <c r="E41">
-        <v>4972.32</v>
+        <v>5006.52</v>
       </c>
       <c r="F41" t="s">
         <v>74</v>
@@ -1797,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>4972.32</v>
+        <v>5006.52</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1808,13 +1808,13 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>395.94</v>
+        <v>403.14</v>
       </c>
       <c r="D42">
-        <v>-385.39</v>
+        <v>122.4</v>
       </c>
       <c r="E42">
-        <v>6730.98</v>
+        <v>6853.38</v>
       </c>
       <c r="F42" t="s">
         <v>74</v>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>6730.98</v>
+        <v>6853.38</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1837,13 +1837,13 @@
         <v>27300</v>
       </c>
       <c r="C43">
-        <v>175.19</v>
+        <v>185.64</v>
       </c>
       <c r="D43">
-        <v>-785694</v>
+        <v>285285</v>
       </c>
       <c r="E43">
-        <v>4782687</v>
+        <v>5067972</v>
       </c>
       <c r="F43" t="s">
         <v>74</v>
@@ -1855,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>4782687</v>
+        <v>5067972</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1866,13 +1866,13 @@
         <v>62</v>
       </c>
       <c r="C44">
-        <v>933.61</v>
+        <v>933.85</v>
       </c>
       <c r="D44">
-        <v>-1842.64</v>
+        <v>14.88</v>
       </c>
       <c r="E44">
-        <v>57883.82</v>
+        <v>57898.7</v>
       </c>
       <c r="F44" t="s">
         <v>74</v>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>57883.82</v>
+        <v>57898.7</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1895,13 +1895,13 @@
         <v>680819</v>
       </c>
       <c r="C45">
-        <v>30.79</v>
+        <v>30.96</v>
       </c>
       <c r="D45">
-        <v>-503806.06</v>
+        <v>115739.23</v>
       </c>
       <c r="E45">
-        <v>20962417.01</v>
+        <v>21078156.24</v>
       </c>
       <c r="F45" t="s">
         <v>74</v>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>20962417.01</v>
+        <v>21078156.24</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1924,13 +1924,13 @@
         <v>42</v>
       </c>
       <c r="C46">
-        <v>141.5</v>
+        <v>139.05</v>
       </c>
       <c r="D46">
-        <v>-23.52</v>
+        <v>-102.9</v>
       </c>
       <c r="E46">
-        <v>5943</v>
+        <v>5840.1</v>
       </c>
       <c r="F46" t="s">
         <v>74</v>
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>5943</v>
+        <v>5840.1</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1953,13 +1953,13 @@
         <v>20</v>
       </c>
       <c r="C47">
-        <v>312.37</v>
+        <v>311.11</v>
       </c>
       <c r="D47">
-        <v>29.6</v>
+        <v>-25.2</v>
       </c>
       <c r="E47">
-        <v>6247.4</v>
+        <v>6222.2</v>
       </c>
       <c r="F47" t="s">
         <v>74</v>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>6247.4</v>
+        <v>6222.2</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1982,13 +1982,13 @@
         <v>333</v>
       </c>
       <c r="C48">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="E48">
-        <v>283.05</v>
+        <v>279.72</v>
       </c>
       <c r="F48" t="s">
         <v>73</v>
@@ -1997,10 +1997,10 @@
         <v>75</v>
       </c>
       <c r="H48">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I48">
-        <v>219.28</v>
+        <v>217.12</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2011,13 +2011,13 @@
         <v>777625</v>
       </c>
       <c r="C49">
-        <v>28.38</v>
+        <v>28.5</v>
       </c>
       <c r="D49">
-        <v>-77762.5</v>
+        <v>93315</v>
       </c>
       <c r="E49">
-        <v>22068997.5</v>
+        <v>22162312.5</v>
       </c>
       <c r="F49" t="s">
         <v>74</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>22068997.5</v>
+        <v>22162312.5</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2040,13 +2040,13 @@
         <v>4000</v>
       </c>
       <c r="C50">
-        <v>610.01</v>
+        <v>709.4400000000001</v>
       </c>
       <c r="D50">
-        <v>-1758760</v>
+        <v>397720</v>
       </c>
       <c r="E50">
-        <v>2440040</v>
+        <v>2837760</v>
       </c>
       <c r="F50" t="s">
         <v>74</v>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>2440040</v>
+        <v>2837760</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2069,13 +2069,13 @@
         <v>1451</v>
       </c>
       <c r="C51">
-        <v>70.17</v>
+        <v>70.36</v>
       </c>
       <c r="D51">
         <v>275.69</v>
       </c>
       <c r="E51">
-        <v>101816.67</v>
+        <v>102092.36</v>
       </c>
       <c r="F51" t="s">
         <v>74</v>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>101816.67</v>
+        <v>102092.36</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2098,13 +2098,13 @@
         <v>1794</v>
       </c>
       <c r="C52">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="D52">
-        <v>-1022.58</v>
+        <v>53.82</v>
       </c>
       <c r="E52">
-        <v>8126.82</v>
+        <v>8180.64</v>
       </c>
       <c r="F52" t="s">
         <v>74</v>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>8126.82</v>
+        <v>8180.64</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2127,13 +2127,13 @@
         <v>3</v>
       </c>
       <c r="C53">
-        <v>1131.42</v>
+        <v>1149.15</v>
       </c>
       <c r="D53">
-        <v>18.45</v>
+        <v>53.19</v>
       </c>
       <c r="E53">
-        <v>3394.26</v>
+        <v>3447.45</v>
       </c>
       <c r="F53" t="s">
         <v>74</v>
@@ -2145,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>3394.26</v>
+        <v>3447.45</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2156,13 +2156,13 @@
         <v>8000</v>
       </c>
       <c r="C54">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="D54">
-        <v>61.98</v>
+        <v>-62.1</v>
       </c>
       <c r="E54">
-        <v>15520</v>
+        <v>15440</v>
       </c>
       <c r="F54" t="s">
         <v>73</v>
@@ -2171,10 +2171,10 @@
         <v>75</v>
       </c>
       <c r="H54">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I54">
-        <v>12023.34</v>
+        <v>11984.53</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2185,13 +2185,13 @@
         <v>1627</v>
       </c>
       <c r="C55">
-        <v>544.4</v>
+        <v>540.8099999999999</v>
       </c>
       <c r="D55">
-        <v>-1252.79</v>
+        <v>-5840.93</v>
       </c>
       <c r="E55">
-        <v>885738.8</v>
+        <v>879897.87</v>
       </c>
       <c r="F55" t="s">
         <v>74</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>885738.8</v>
+        <v>879897.87</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2214,13 +2214,13 @@
         <v>50</v>
       </c>
       <c r="C56">
-        <v>42.96</v>
+        <v>41.02</v>
       </c>
       <c r="D56">
-        <v>-39.5</v>
+        <v>-97</v>
       </c>
       <c r="E56">
-        <v>2148</v>
+        <v>2051</v>
       </c>
       <c r="F56" t="s">
         <v>74</v>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>2148</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2243,13 +2243,13 @@
         <v>100</v>
       </c>
       <c r="C57">
-        <v>60.84</v>
+        <v>60.01</v>
       </c>
       <c r="D57">
-        <v>109</v>
+        <v>-83</v>
       </c>
       <c r="E57">
-        <v>6084</v>
+        <v>6001</v>
       </c>
       <c r="F57" t="s">
         <v>74</v>
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>6084</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2272,13 +2272,13 @@
         <v>34</v>
       </c>
       <c r="C58">
-        <v>272.05</v>
+        <v>266.33</v>
       </c>
       <c r="D58">
-        <v>-244.8</v>
+        <v>-194.48</v>
       </c>
       <c r="E58">
-        <v>9249.700000000001</v>
+        <v>9055.219999999999</v>
       </c>
       <c r="F58" t="s">
         <v>74</v>
@@ -2290,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>9249.700000000001</v>
+        <v>9055.219999999999</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2301,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="C59">
-        <v>103.633</v>
+        <v>102.54</v>
       </c>
       <c r="D59">
-        <v>-20.14</v>
+        <v>-10.93</v>
       </c>
       <c r="E59">
-        <v>1036.33</v>
+        <v>1025.4</v>
       </c>
       <c r="F59" t="s">
         <v>74</v>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>1036.33</v>
+        <v>1025.4</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2330,13 +2330,13 @@
         <v>29160</v>
       </c>
       <c r="C60">
-        <v>705.0599999999999</v>
+        <v>716.0700000000001</v>
       </c>
       <c r="D60">
-        <v>-1036638</v>
+        <v>321051.6</v>
       </c>
       <c r="E60">
-        <v>20559549.6</v>
+        <v>20880601.2</v>
       </c>
       <c r="F60" t="s">
         <v>74</v>
@@ -2348,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>20559549.6</v>
+        <v>20880601.2</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2359,13 +2359,13 @@
         <v>4320</v>
       </c>
       <c r="C61">
-        <v>180.99</v>
+        <v>178.66</v>
       </c>
       <c r="D61">
-        <v>6825.6</v>
+        <v>-10065.6</v>
       </c>
       <c r="E61">
-        <v>781876.8</v>
+        <v>771811.2</v>
       </c>
       <c r="F61" t="s">
         <v>74</v>
@@ -2377,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>781876.8</v>
+        <v>771811.2</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2388,13 +2388,13 @@
         <v>66900</v>
       </c>
       <c r="C62">
-        <v>21.74</v>
+        <v>21.44</v>
       </c>
       <c r="D62">
-        <v>-7256.12</v>
+        <v>-15578.13</v>
       </c>
       <c r="E62">
-        <v>1454406</v>
+        <v>1434336</v>
       </c>
       <c r="F62" t="s">
         <v>73</v>
@@ -2403,10 +2403,10 @@
         <v>75</v>
       </c>
       <c r="H62">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I62">
-        <v>1126728.33</v>
+        <v>1113331.6</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2417,13 +2417,13 @@
         <v>8200</v>
       </c>
       <c r="C63">
-        <v>103.31</v>
+        <v>103.77</v>
       </c>
       <c r="D63">
-        <v>-17712</v>
+        <v>3772</v>
       </c>
       <c r="E63">
-        <v>847142</v>
+        <v>850914</v>
       </c>
       <c r="F63" t="s">
         <v>74</v>
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>847142</v>
+        <v>850914</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2446,13 +2446,13 @@
         <v>100</v>
       </c>
       <c r="C64">
-        <v>63.05</v>
+        <v>63.07</v>
       </c>
       <c r="D64">
-        <v>-126</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>6305</v>
+        <v>6307</v>
       </c>
       <c r="F64" t="s">
         <v>74</v>
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>6305</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2475,13 +2475,13 @@
         <v>20100</v>
       </c>
       <c r="C65">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="D65">
-        <v>-7839</v>
+        <v>-1005</v>
       </c>
       <c r="E65">
-        <v>69747</v>
+        <v>68742</v>
       </c>
       <c r="F65" t="s">
         <v>74</v>
@@ -2493,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>69747</v>
+        <v>68742</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2504,13 +2504,13 @@
         <v>2</v>
       </c>
       <c r="C66">
-        <v>262.56</v>
+        <v>264.53</v>
       </c>
       <c r="D66">
-        <v>-45</v>
+        <v>3.94</v>
       </c>
       <c r="E66">
-        <v>525.12</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="F66" t="s">
         <v>74</v>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>525.12</v>
+        <v>529.0599999999999</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2533,13 +2533,13 @@
         <v>51700</v>
       </c>
       <c r="C67">
-        <v>38.55</v>
+        <v>37.79</v>
       </c>
       <c r="D67">
-        <v>9612.85</v>
+        <v>-30498.06</v>
       </c>
       <c r="E67">
-        <v>1993035</v>
+        <v>1953743</v>
       </c>
       <c r="F67" t="s">
         <v>73</v>
@@ -2548,10 +2548,10 @@
         <v>75</v>
       </c>
       <c r="H67">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I67">
-        <v>1544004.21</v>
+        <v>1516495.32</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2562,13 +2562,13 @@
         <v>534400</v>
       </c>
       <c r="C68">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
       <c r="D68">
-        <v>-33121.26</v>
+        <v>-29035.72</v>
       </c>
       <c r="E68">
-        <v>3275872</v>
+        <v>3238464</v>
       </c>
       <c r="F68" t="s">
         <v>73</v>
@@ -2577,10 +2577,10 @@
         <v>75</v>
       </c>
       <c r="H68">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I68">
-        <v>2537818.04</v>
+        <v>2513695.76</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2591,13 +2591,13 @@
         <v>1</v>
       </c>
       <c r="C69">
-        <v>95.64</v>
+        <v>95.23</v>
       </c>
       <c r="D69">
-        <v>-1.02</v>
+        <v>-0.41</v>
       </c>
       <c r="E69">
-        <v>95.64</v>
+        <v>95.23</v>
       </c>
       <c r="F69" t="s">
         <v>74</v>
@@ -2609,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>95.64</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2620,13 +2620,13 @@
         <v>10</v>
       </c>
       <c r="C70">
-        <v>162.36</v>
+        <v>164.43</v>
       </c>
       <c r="D70">
-        <v>-35</v>
+        <v>20.7</v>
       </c>
       <c r="E70">
-        <v>1623.6</v>
+        <v>1644.3</v>
       </c>
       <c r="F70" t="s">
         <v>74</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>1623.6</v>
+        <v>1644.3</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2649,13 +2649,13 @@
         <v>1000</v>
       </c>
       <c r="C71">
-        <v>24.69</v>
+        <v>24.2101</v>
       </c>
       <c r="D71">
-        <v>-136</v>
+        <v>-479.9</v>
       </c>
       <c r="E71">
-        <v>24690</v>
+        <v>24210.1</v>
       </c>
       <c r="F71" t="s">
         <v>74</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>24690</v>
+        <v>24210.1</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2678,13 +2678,13 @@
         <v>21</v>
       </c>
       <c r="C72">
-        <v>300.51</v>
+        <v>300.57</v>
       </c>
       <c r="D72">
-        <v>-491.61</v>
+        <v>1.26</v>
       </c>
       <c r="E72">
-        <v>6310.71</v>
+        <v>6311.97</v>
       </c>
       <c r="F72" t="s">
         <v>74</v>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>6310.71</v>
+        <v>6311.97</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2707,13 +2707,13 @@
         <v>10</v>
       </c>
       <c r="C73">
-        <v>148.76</v>
+        <v>146.9</v>
       </c>
       <c r="D73">
-        <v>-49.4</v>
+        <v>-18.6</v>
       </c>
       <c r="E73">
-        <v>1487.6</v>
+        <v>1469</v>
       </c>
       <c r="F73" t="s">
         <v>74</v>
@@ -2725,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>1487.6</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2736,13 +2736,13 @@
         <v>6003</v>
       </c>
       <c r="C74">
-        <v>45.37</v>
+        <v>45.44</v>
       </c>
       <c r="D74">
-        <v>3001.5</v>
+        <v>420.21</v>
       </c>
       <c r="E74">
-        <v>272356.11</v>
+        <v>272776.32</v>
       </c>
       <c r="F74" t="s">
         <v>74</v>
@@ -2754,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>272356.11</v>
+        <v>272776.32</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2765,13 +2765,13 @@
         <v>218100</v>
       </c>
       <c r="C75">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="D75">
-        <v>-5069.06</v>
+        <v>-13542.96</v>
       </c>
       <c r="E75">
-        <v>935649</v>
+        <v>918201</v>
       </c>
       <c r="F75" t="s">
         <v>73</v>
@@ -2780,10 +2780,10 @@
         <v>75</v>
       </c>
       <c r="H75">
-        <v>0.7747000000000001</v>
+        <v>0.7762</v>
       </c>
       <c r="I75">
-        <v>724847.28</v>
+        <v>712707.62</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2794,13 +2794,13 @@
         <v>484670</v>
       </c>
       <c r="C76">
-        <v>100.45</v>
+        <v>100.46</v>
       </c>
       <c r="D76">
-        <v>14540.1</v>
+        <v>4846.7</v>
       </c>
       <c r="E76">
-        <v>48685101.5</v>
+        <v>48689948.2</v>
       </c>
       <c r="F76" t="s">
         <v>74</v>
@@ -2812,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>48685101.5</v>
+        <v>48689948.2</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2823,13 +2823,13 @@
         <v>1521</v>
       </c>
       <c r="C77">
-        <v>42.17</v>
+        <v>42.19</v>
       </c>
       <c r="D77">
-        <v>-197.73</v>
+        <v>30.42</v>
       </c>
       <c r="E77">
-        <v>64140.57</v>
+        <v>64170.99</v>
       </c>
       <c r="F77" t="s">
         <v>74</v>
@@ -2841,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>64140.57</v>
+        <v>64170.99</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2849,16 +2849,16 @@
         <v>68</v>
       </c>
       <c r="B78">
-        <v>36428</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>43.02</v>
+        <v>43.11</v>
       </c>
       <c r="D78">
-        <v>-59013.36</v>
+        <v>5054.38</v>
       </c>
       <c r="E78">
-        <v>1567132.56</v>
+        <v>0</v>
       </c>
       <c r="F78" t="s">
         <v>74</v>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>1567132.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2881,13 +2881,13 @@
         <v>100</v>
       </c>
       <c r="C79">
-        <v>78.81999999999999</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="D79">
-        <v>-15</v>
+        <v>-125</v>
       </c>
       <c r="E79">
-        <v>7882</v>
+        <v>7757</v>
       </c>
       <c r="F79" t="s">
         <v>74</v>
@@ -2899,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>7882</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2910,13 +2910,13 @@
         <v>33</v>
       </c>
       <c r="C80">
-        <v>57.31</v>
+        <v>57.28</v>
       </c>
       <c r="D80">
-        <v>-1.32</v>
+        <v>-0.99</v>
       </c>
       <c r="E80">
-        <v>1891.23</v>
+        <v>1890.24</v>
       </c>
       <c r="F80" t="s">
         <v>74</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>1891.23</v>
+        <v>1890.24</v>
       </c>
     </row>
   </sheetData>
